--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -44,9 +44,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -58,13 +58,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -72,61 +93,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,24 +117,31 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -187,15 +163,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,31 +210,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,13 +348,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -264,133 +378,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +401,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -424,17 +415,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -465,6 +445,32 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -487,17 +493,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1293,7 +1293,7 @@
         <v>8040</v>
       </c>
       <c r="E14">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>8040</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>8010</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>8010</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>11002</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>11000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1460,291 +1460,291 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>8010</v>
+        <v>8040</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>14023</v>
+        <v>15063</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>311</v>
+        <v>241</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>8010</v>
+        <v>8040</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>800</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>14025</v>
+        <v>15062</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>320</v>
+        <v>242</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>8020</v>
+        <v>8040</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>11002</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>11000</v>
+        <v>14033</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>8030</v>
+        <v>8010</v>
       </c>
       <c r="E26">
-        <v>6500</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>50</v>
+        <v>14030</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E27">
-        <v>5500</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>410</v>
+        <v>321</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>14033</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>8500</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>14035</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>420</v>
+        <v>331</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>7500</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>12000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>421</v>
+        <v>340</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>8020</v>
+        <v>8040</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>11002</v>
+        <v>15063</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>430</v>
+        <v>341</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>8030</v>
+        <v>8040</v>
       </c>
       <c r="E32">
-        <v>6500</v>
+        <v>800</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>50</v>
+        <v>15062</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>431</v>
+        <v>342</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>8030</v>
+        <v>8040</v>
       </c>
       <c r="E33">
-        <v>5500</v>
+        <v>500</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>25</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>511</v>
+        <v>411</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>521</v>
+        <v>421</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>530</v>
+        <v>430</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>531</v>
+        <v>431</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -1874,6 +1874,144 @@
         <v>0</v>
       </c>
       <c r="G39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>510</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>8010</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>14033</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>511</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>8010</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>14035</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>520</v>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>8020</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>521</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>8020</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>530</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
+        <v>8030</v>
+      </c>
+      <c r="E44">
+        <v>6500</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>531</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45">
+        <v>8030</v>
+      </c>
+      <c r="E45">
+        <v>5500</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>25</v>
       </c>
     </row>
